--- a/blendmaster_OOP/output/expit_payload_transactions.xlsx
+++ b/blendmaster_OOP/output/expit_payload_transactions.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>45624.25</v>
+        <v>45646.61370050871</v>
       </c>
       <c r="F2" t="n">
         <v>240</v>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>45624.26448056725</v>
+        <v>45646.62818107596</v>
       </c>
     </row>
     <row r="3">
@@ -559,7 +559,7 @@
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>45624.25489267677</v>
+        <v>45646.61859318549</v>
       </c>
       <c r="F3" t="n">
         <v>187.4745180802211</v>
@@ -585,7 +585,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>45624.26937324402</v>
+        <v>45646.63307375273</v>
       </c>
     </row>
     <row r="4">
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>45624.25565867001</v>
+        <v>45646.61935917872</v>
       </c>
       <c r="F4" t="n">
         <v>240</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>45624.26976834812</v>
+        <v>45646.63346885684</v>
       </c>
     </row>
     <row r="5">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>45624.26055134678</v>
+        <v>45646.6242518555</v>
       </c>
       <c r="F5" t="n">
         <v>240</v>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>45624.27466102489</v>
+        <v>45646.63836153361</v>
       </c>
     </row>
     <row r="6">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>45624.26544402356</v>
+        <v>45646.62914453227</v>
       </c>
       <c r="F6" t="n">
         <v>240</v>
@@ -726,7 +726,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>45624.27955370166</v>
+        <v>45646.64325421038</v>
       </c>
     </row>
     <row r="7">
@@ -747,7 +747,7 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>45624.27033670033</v>
+        <v>45646.63403720904</v>
       </c>
       <c r="F7" t="n">
         <v>240</v>
@@ -773,7 +773,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>45624.28444637843</v>
+        <v>45646.64814688715</v>
       </c>
     </row>
     <row r="8">
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>45624.2752293771</v>
+        <v>45646.63892988581</v>
       </c>
       <c r="F8" t="n">
         <v>240</v>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>45624.28933905521</v>
+        <v>45646.65303956392</v>
       </c>
     </row>
     <row r="9">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="E9" s="2" t="n">
-        <v>45624.28012205387</v>
+        <v>45646.64382256258</v>
       </c>
       <c r="F9" t="n">
         <v>240</v>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>45624.29423173198</v>
+        <v>45646.6579322407</v>
       </c>
     </row>
     <row r="10">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="E10" s="2" t="n">
-        <v>45624.28501473064</v>
+        <v>45646.64871523935</v>
       </c>
       <c r="F10" t="n">
         <v>240</v>
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>45624.29912440875</v>
+        <v>45646.66282491747</v>
       </c>
     </row>
     <row r="11">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>45624.28990740741</v>
+        <v>45646.65360791612</v>
       </c>
       <c r="F11" t="n">
         <v>240</v>
@@ -961,7 +961,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>45624.30401708552</v>
+        <v>45646.66771759424</v>
       </c>
     </row>
     <row r="12">
@@ -982,7 +982,7 @@
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>45624.29480008418</v>
+        <v>45646.65850059289</v>
       </c>
       <c r="F12" t="n">
         <v>240</v>
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>45624.30890976229</v>
+        <v>45646.67261027101</v>
       </c>
     </row>
     <row r="13">
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>45624.29969276095</v>
+        <v>45646.66339326966</v>
       </c>
       <c r="F13" t="n">
         <v>240</v>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>45624.31380243906</v>
+        <v>45646.67750294778</v>
       </c>
     </row>
     <row r="14">
@@ -1076,7 +1076,7 @@
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>45624.30458543772</v>
+        <v>45646.66828594643</v>
       </c>
       <c r="F14" t="n">
         <v>240</v>
@@ -1102,7 +1102,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>45624.31869511583</v>
+        <v>45646.68239562455</v>
       </c>
     </row>
     <row r="15">
@@ -1123,7 +1123,7 @@
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>45624.30947811449</v>
+        <v>45646.6731786232</v>
       </c>
       <c r="F15" t="n">
         <v>240</v>
@@ -1149,7 +1149,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>45624.32358779261</v>
+        <v>45646.68728830132</v>
       </c>
     </row>
     <row r="16">
@@ -1170,7 +1170,7 @@
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>45624.31437079126</v>
+        <v>45646.67807129998</v>
       </c>
       <c r="F16" t="n">
         <v>240</v>
@@ -1196,7 +1196,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>45624.32848046938</v>
+        <v>45646.69218097809</v>
       </c>
     </row>
     <row r="17">
@@ -1217,7 +1217,7 @@
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>45624.31926346803</v>
+        <v>45646.68296397675</v>
       </c>
       <c r="F17" t="n">
         <v>240</v>
@@ -1243,7 +1243,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>45624.33337314615</v>
+        <v>45646.69707365486</v>
       </c>
     </row>
     <row r="18">
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>45624.3241561448</v>
+        <v>45646.68785665352</v>
       </c>
       <c r="F18" t="n">
         <v>240</v>
@@ -1290,7 +1290,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>45624.33826582292</v>
+        <v>45646.70196633163</v>
       </c>
     </row>
     <row r="19">
@@ -1311,7 +1311,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>45624.32904882157</v>
+        <v>45646.69274933029</v>
       </c>
       <c r="F19" t="n">
         <v>240</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>45624.34315849969</v>
+        <v>45646.7068590084</v>
       </c>
     </row>
     <row r="20">
@@ -1358,7 +1358,7 @@
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>45624.33394149834</v>
+        <v>45646.69764200706</v>
       </c>
       <c r="F20" t="n">
         <v>240</v>
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>45624.34805117646</v>
+        <v>45646.71175168517</v>
       </c>
     </row>
     <row r="21">
@@ -1405,7 +1405,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>45624.33591329964</v>
+        <v>45646.69961380836</v>
       </c>
       <c r="F21" t="n">
         <v>240</v>
@@ -1431,7 +1431,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>45624.3503712759</v>
+        <v>45646.71407178462</v>
       </c>
     </row>
     <row r="22">
@@ -1452,7 +1452,7 @@
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>45624.33883417511</v>
+        <v>45646.70253468383</v>
       </c>
       <c r="F22" t="n">
         <v>157.3038506492303</v>
@@ -1478,7 +1478,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>45624.35294385323</v>
+        <v>45646.71664436194</v>
       </c>
     </row>
     <row r="23">
@@ -1499,7 +1499,7 @@
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>45624.34080597641</v>
+        <v>45646.70450648513</v>
       </c>
       <c r="F23" t="n">
         <v>240</v>
@@ -1525,7 +1525,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>45624.35526395268</v>
+        <v>45646.71896446139</v>
       </c>
     </row>
     <row r="24">
@@ -1546,7 +1546,7 @@
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>45624.34569865318</v>
+        <v>45646.7093991619</v>
       </c>
       <c r="F24" t="n">
         <v>240</v>
@@ -1572,7 +1572,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>45624.36015662945</v>
+        <v>45646.72385713816</v>
       </c>
     </row>
     <row r="25">
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>45624.35059132995</v>
+        <v>45646.71429183867</v>
       </c>
       <c r="F25" t="n">
         <v>240</v>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>45624.36504930622</v>
+        <v>45646.72874981493</v>
       </c>
     </row>
     <row r="26">
@@ -1640,7 +1640,7 @@
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>45624.35548400672</v>
+        <v>45646.71918451544</v>
       </c>
       <c r="F26" t="n">
         <v>240</v>
@@ -1666,7 +1666,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>45624.36994198299</v>
+        <v>45646.7336424917</v>
       </c>
     </row>
     <row r="27">
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>45624.36037668349</v>
+        <v>45646.72407719221</v>
       </c>
       <c r="F27" t="n">
         <v>240</v>
@@ -1713,7 +1713,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>45624.37483465976</v>
+        <v>45646.73853516847</v>
       </c>
     </row>
     <row r="28">
@@ -1734,7 +1734,7 @@
         </is>
       </c>
       <c r="E28" s="2" t="n">
-        <v>45624.36526936026</v>
+        <v>45646.72896986898</v>
       </c>
       <c r="F28" t="n">
         <v>240</v>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>45624.37972733653</v>
+        <v>45646.74342784524</v>
       </c>
     </row>
     <row r="29">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="E29" s="2" t="n">
-        <v>45624.37016203703</v>
+        <v>45646.73386254575</v>
       </c>
       <c r="F29" t="n">
         <v>240</v>
@@ -1807,7 +1807,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>45624.3846200133</v>
+        <v>45646.74832052201</v>
       </c>
     </row>
     <row r="30">
@@ -1828,7 +1828,7 @@
         </is>
       </c>
       <c r="E30" s="2" t="n">
-        <v>45624.41347117001</v>
+        <v>45646.77717167872</v>
       </c>
       <c r="F30" t="n">
         <v>240</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>45624.42792653513</v>
+        <v>45646.79162704384</v>
       </c>
     </row>
     <row r="31">
@@ -1875,7 +1875,7 @@
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>45624.41836384678</v>
+        <v>45646.7820643555</v>
       </c>
       <c r="F31" t="n">
         <v>240</v>
@@ -1901,7 +1901,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>45624.4328192119</v>
+        <v>45646.79651972061</v>
       </c>
     </row>
     <row r="32">
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>45624.42325652355</v>
+        <v>45646.78695703227</v>
       </c>
       <c r="F32" t="n">
         <v>240</v>
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>45624.43771188867</v>
+        <v>45646.80141239738</v>
       </c>
     </row>
     <row r="33">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>45624.42628367001</v>
+        <v>45646.78998417873</v>
       </c>
       <c r="F33" t="n">
         <v>240</v>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>45624.44072590146</v>
+        <v>45646.80442641017</v>
       </c>
     </row>
     <row r="34">
@@ -2016,7 +2016,7 @@
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>45624.43117634678</v>
+        <v>45646.7948768555</v>
       </c>
       <c r="F34" t="n">
         <v>240</v>
@@ -2042,7 +2042,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>45624.44561857823</v>
+        <v>45646.80931908695</v>
       </c>
     </row>
     <row r="35">
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>45624.43606902356</v>
+        <v>45646.79976953227</v>
       </c>
       <c r="F35" t="n">
         <v>240</v>
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>45624.450511255</v>
+        <v>45646.81421176372</v>
       </c>
     </row>
     <row r="36">
@@ -2110,7 +2110,7 @@
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>45624.44096170033</v>
+        <v>45646.80466220904</v>
       </c>
       <c r="F36" t="n">
         <v>240</v>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>45624.45540393177</v>
+        <v>45646.81910444049</v>
       </c>
     </row>
     <row r="37">
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>45624.4458543771</v>
+        <v>45646.80955488581</v>
       </c>
       <c r="F37" t="n">
         <v>240</v>
@@ -2183,7 +2183,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>45624.46029660854</v>
+        <v>45646.82399711726</v>
       </c>
     </row>
     <row r="38">
@@ -2204,7 +2204,7 @@
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>45624.45074705387</v>
+        <v>45646.81444756258</v>
       </c>
       <c r="F38" t="n">
         <v>240</v>
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>45624.46518928531</v>
+        <v>45646.82888979403</v>
       </c>
     </row>
     <row r="39">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>45624.45563973064</v>
+        <v>45646.81934023935</v>
       </c>
       <c r="F39" t="n">
         <v>240</v>
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>45624.47008196208</v>
+        <v>45646.8337824708</v>
       </c>
     </row>
     <row r="40">
@@ -2298,7 +2298,7 @@
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>45624.46053240741</v>
+        <v>45646.82423291612</v>
       </c>
       <c r="F40" t="n">
         <v>240</v>
@@ -2324,7 +2324,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>45624.47497463886</v>
+        <v>45646.83867514757</v>
       </c>
     </row>
     <row r="41">
@@ -2345,7 +2345,7 @@
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>45624.46542508418</v>
+        <v>45646.82912559289</v>
       </c>
       <c r="F41" t="n">
         <v>240</v>
@@ -2371,7 +2371,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>45624.47986731563</v>
+        <v>45646.84356782434</v>
       </c>
     </row>
     <row r="42">
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>45624.47031776095</v>
+        <v>45646.83401826966</v>
       </c>
       <c r="F42" t="n">
         <v>240</v>
@@ -2418,7 +2418,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>45624.4847599924</v>
+        <v>45646.84846050111</v>
       </c>
     </row>
     <row r="43">
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>45624.47521043772</v>
+        <v>45646.83891094643</v>
       </c>
       <c r="F43" t="n">
         <v>240</v>
@@ -2465,7 +2465,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>45624.48965266917</v>
+        <v>45646.85335317788</v>
       </c>
     </row>
     <row r="44">
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="E44" s="2" t="n">
-        <v>45624.48010311449</v>
+        <v>45646.8438036232</v>
       </c>
       <c r="F44" t="n">
         <v>240</v>
@@ -2512,7 +2512,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>45624.49454534594</v>
+        <v>45646.85824585465</v>
       </c>
     </row>
     <row r="45">
@@ -2533,7 +2533,7 @@
         </is>
       </c>
       <c r="E45" s="2" t="n">
-        <v>45624.48499579126</v>
+        <v>45646.84869629997</v>
       </c>
       <c r="F45" t="n">
         <v>240</v>
@@ -2559,7 +2559,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>45624.49943802271</v>
+        <v>45646.86313853142</v>
       </c>
     </row>
     <row r="46">
@@ -2580,7 +2580,7 @@
         </is>
       </c>
       <c r="E46" s="2" t="n">
-        <v>45624.48988846803</v>
+        <v>45646.85358897674</v>
       </c>
       <c r="F46" t="n">
         <v>240</v>
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>45624.50433069948</v>
+        <v>45646.86803120819</v>
       </c>
     </row>
     <row r="47">
@@ -2627,7 +2627,7 @@
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>45624.4947811448</v>
+        <v>45646.85848165351</v>
       </c>
       <c r="F47" t="n">
         <v>240</v>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>45624.50922337625</v>
+        <v>45646.87292388496</v>
       </c>
     </row>
     <row r="48">
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>45624.49967382157</v>
+        <v>45646.86337433029</v>
       </c>
       <c r="F48" t="n">
         <v>240</v>
@@ -2700,7 +2700,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>45624.51411605302</v>
+        <v>45646.87781656173</v>
       </c>
     </row>
     <row r="49">
@@ -2721,7 +2721,7 @@
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>45624.50456649835</v>
+        <v>45646.86826700706</v>
       </c>
       <c r="F49" t="n">
         <v>240</v>
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>45624.51900872979</v>
+        <v>45646.8827092385</v>
       </c>
     </row>
     <row r="50">
@@ -2768,7 +2768,7 @@
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>45624.50707070705</v>
+        <v>45646.87077121576</v>
       </c>
       <c r="F50" t="n">
         <v>240</v>
@@ -2794,7 +2794,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>45624.52127136104</v>
+        <v>45646.88497186976</v>
       </c>
     </row>
     <row r="51">
@@ -2815,7 +2815,7 @@
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>45624.50945917512</v>
+        <v>45646.87315968383</v>
       </c>
       <c r="F51" t="n">
         <v>117.3795346235511</v>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>45624.52390140656</v>
+        <v>45646.88760191528</v>
       </c>
     </row>
     <row r="52">
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>45624.51196338382</v>
+        <v>45646.87566389253</v>
       </c>
       <c r="F52" t="n">
         <v>240</v>
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>45624.52616403782</v>
+        <v>45646.88986454653</v>
       </c>
     </row>
     <row r="53">
@@ -2909,7 +2909,7 @@
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>45624.51685606059</v>
+        <v>45646.8805565693</v>
       </c>
       <c r="F53" t="n">
         <v>240</v>
@@ -2935,7 +2935,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>45624.53105671459</v>
+        <v>45646.8947572233</v>
       </c>
     </row>
     <row r="54">
@@ -2956,7 +2956,7 @@
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>45624.52174873736</v>
+        <v>45646.88544924607</v>
       </c>
       <c r="F54" t="n">
         <v>240</v>
@@ -2982,7 +2982,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>45624.53594939136</v>
+        <v>45646.89964990007</v>
       </c>
     </row>
     <row r="55">
@@ -3003,7 +3003,7 @@
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>45624.52664141413</v>
+        <v>45646.89034192284</v>
       </c>
       <c r="F55" t="n">
         <v>240</v>
@@ -3029,7 +3029,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>45624.54084206813</v>
+        <v>45646.90454257684</v>
       </c>
     </row>
     <row r="56">
@@ -3050,7 +3050,7 @@
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>45624.5315340909</v>
+        <v>45646.89523459961</v>
       </c>
       <c r="F56" t="n">
         <v>240</v>
@@ -3076,7 +3076,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>45624.5457347449</v>
+        <v>45646.90943525361</v>
       </c>
     </row>
     <row r="57">
@@ -3097,7 +3097,7 @@
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>45624.53642676767</v>
+        <v>45646.90012727639</v>
       </c>
       <c r="F57" t="n">
         <v>240</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>45624.55062742167</v>
+        <v>45646.91432793038</v>
       </c>
     </row>
     <row r="58">
@@ -3144,7 +3144,7 @@
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>45624.55542718853</v>
+        <v>45646.91912769725</v>
       </c>
       <c r="F58" t="n">
         <v>240</v>
@@ -3170,7 +3170,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>45624.56968147074</v>
+        <v>45646.93338197946</v>
       </c>
     </row>
     <row r="59">
@@ -3191,7 +3191,7 @@
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>45624.5603198653</v>
+        <v>45646.92402037402</v>
       </c>
       <c r="F59" t="n">
         <v>240</v>
@@ -3217,7 +3217,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>45624.57457414751</v>
+        <v>45646.93827465623</v>
       </c>
     </row>
     <row r="60">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>45624.56521254207</v>
+        <v>45646.92891305079</v>
       </c>
       <c r="F60" t="n">
         <v>240</v>
@@ -3264,7 +3264,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>45624.57946682428</v>
+        <v>45646.943167333</v>
       </c>
     </row>
     <row r="61">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>45624.57010521885</v>
+        <v>45646.93380572756</v>
       </c>
       <c r="F61" t="n">
         <v>240</v>
@@ -3311,7 +3311,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>45624.58435950105</v>
+        <v>45646.94806000977</v>
       </c>
     </row>
     <row r="62">
@@ -3332,7 +3332,7 @@
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>45624.57499789562</v>
+        <v>45646.93869840433</v>
       </c>
       <c r="F62" t="n">
         <v>240</v>
@@ -3358,7 +3358,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>45624.58925217782</v>
+        <v>45646.95295268654</v>
       </c>
     </row>
     <row r="63">
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>45624.57989057239</v>
+        <v>45646.9435910811</v>
       </c>
       <c r="F63" t="n">
         <v>240</v>
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>45624.59414485459</v>
+        <v>45646.95784536331</v>
       </c>
     </row>
     <row r="64">
@@ -3426,7 +3426,7 @@
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>45624.58478324916</v>
+        <v>45646.94848375787</v>
       </c>
       <c r="F64" t="n">
         <v>240</v>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>45624.59903753136</v>
+        <v>45646.96273804008</v>
       </c>
     </row>
     <row r="65">
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>45624.58967592593</v>
+        <v>45646.95337643464</v>
       </c>
       <c r="F65" t="n">
         <v>240</v>
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>45624.60393020813</v>
+        <v>45646.96763071685</v>
       </c>
     </row>
     <row r="66">
@@ -3520,7 +3520,7 @@
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>45624.5945686027</v>
+        <v>45646.95826911141</v>
       </c>
       <c r="F66" t="n">
         <v>240</v>
@@ -3546,7 +3546,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>45624.6088228849</v>
+        <v>45646.97252339363</v>
       </c>
     </row>
     <row r="67">
@@ -3567,7 +3567,7 @@
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>45624.59946127947</v>
+        <v>45646.96316178818</v>
       </c>
       <c r="F67" t="n">
         <v>240</v>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>45624.61371556168</v>
+        <v>45646.9774160704</v>
       </c>
     </row>
     <row r="68">
@@ -3614,7 +3614,7 @@
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>45624.60435395624</v>
+        <v>45646.96805446495</v>
       </c>
       <c r="F68" t="n">
         <v>240</v>
@@ -3640,7 +3640,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>45624.61860823845</v>
+        <v>45646.98230874717</v>
       </c>
     </row>
     <row r="69">
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>45624.60924663301</v>
+        <v>45646.97294714172</v>
       </c>
       <c r="F69" t="n">
         <v>240</v>
@@ -3687,7 +3687,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>45624.62350091522</v>
+        <v>45646.98720142394</v>
       </c>
     </row>
     <row r="70">
@@ -3708,7 +3708,7 @@
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>45624.61413930978</v>
+        <v>45646.97783981849</v>
       </c>
       <c r="F70" t="n">
         <v>240</v>
@@ -3734,7 +3734,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>45624.62839359199</v>
+        <v>45646.99209410071</v>
       </c>
     </row>
     <row r="71">
@@ -3755,7 +3755,7 @@
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>45624.61903198655</v>
+        <v>45646.98273249526</v>
       </c>
       <c r="F71" t="n">
         <v>240</v>
@@ -3781,7 +3781,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>45624.63328626876</v>
+        <v>45646.99698677748</v>
       </c>
     </row>
     <row r="72">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>45624.62392466332</v>
+        <v>45646.98762517203</v>
       </c>
       <c r="F72" t="n">
         <v>240</v>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>45624.63817894553</v>
+        <v>45647.00187945425</v>
       </c>
     </row>
     <row r="73">
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>45624.62881734009</v>
+        <v>45646.9925178488</v>
       </c>
       <c r="F73" t="n">
         <v>240</v>
@@ -3875,7 +3875,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>45624.6430716223</v>
+        <v>45647.00677213102</v>
       </c>
     </row>
     <row r="74">
@@ -3896,7 +3896,7 @@
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>45624.63371001686</v>
+        <v>45646.99741052558</v>
       </c>
       <c r="F74" t="n">
         <v>240</v>
@@ -3922,7 +3922,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>45624.64796429907</v>
+        <v>45647.01166480779</v>
       </c>
     </row>
     <row r="75">
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>45624.63860269363</v>
+        <v>45647.00230320235</v>
       </c>
       <c r="F75" t="n">
         <v>240</v>
@@ -3969,7 +3969,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>45624.65285697584</v>
+        <v>45647.01655748456</v>
       </c>
     </row>
     <row r="76">
@@ -3990,7 +3990,7 @@
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>45624.64349537041</v>
+        <v>45647.00719587912</v>
       </c>
       <c r="F76" t="n">
         <v>240</v>
@@ -4016,7 +4016,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>45624.65774965262</v>
+        <v>45647.02145016133</v>
       </c>
     </row>
     <row r="77">
@@ -4037,7 +4037,7 @@
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>45624.64838804718</v>
+        <v>45647.01208855589</v>
       </c>
       <c r="F77" t="n">
         <v>240</v>
@@ -4063,7 +4063,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>45624.66264232939</v>
+        <v>45647.0263428381</v>
       </c>
     </row>
     <row r="78">
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>45624.65168876261</v>
+        <v>45647.01538927132</v>
       </c>
       <c r="F78" t="n">
         <v>240</v>
@@ -4110,7 +4110,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>45624.66602814309</v>
+        <v>45647.0297286518</v>
       </c>
     </row>
     <row r="79">
@@ -4131,7 +4131,7 @@
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>45624.65328072395</v>
+        <v>45647.01698123266</v>
       </c>
       <c r="F79" t="n">
         <v>240</v>
@@ -4157,7 +4157,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>45624.66753500616</v>
+        <v>45647.03123551487</v>
       </c>
     </row>
     <row r="80">
@@ -4178,7 +4178,7 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>45624.65658143938</v>
+        <v>45647.02028194809</v>
       </c>
       <c r="F80" t="n">
         <v>240</v>
@@ -4204,7 +4204,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>45624.67092081986</v>
+        <v>45647.03462132857</v>
       </c>
     </row>
     <row r="81">
@@ -4225,7 +4225,7 @@
         </is>
       </c>
       <c r="E81" s="2" t="n">
-        <v>45624.66147411615</v>
+        <v>45647.02517462486</v>
       </c>
       <c r="F81" t="n">
         <v>240</v>
@@ -4251,7 +4251,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>45624.67581349663</v>
+        <v>45647.03951400534</v>
       </c>
     </row>
     <row r="82">
@@ -4272,7 +4272,7 @@
         </is>
       </c>
       <c r="E82" s="2" t="n">
-        <v>45624.66636679292</v>
+        <v>45647.03006730163</v>
       </c>
       <c r="F82" t="n">
         <v>240</v>
@@ -4298,7 +4298,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>45624.6807061734</v>
+        <v>45647.04440668211</v>
       </c>
     </row>
     <row r="83">
@@ -4319,7 +4319,7 @@
         </is>
       </c>
       <c r="E83" s="2" t="n">
-        <v>45624.67125946969</v>
+        <v>45647.0349599784</v>
       </c>
       <c r="F83" t="n">
         <v>240</v>
@@ -4345,7 +4345,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>45624.68559885017</v>
+        <v>45647.04929935889</v>
       </c>
     </row>
     <row r="84">
@@ -4366,7 +4366,7 @@
         </is>
       </c>
       <c r="E84" s="2" t="n">
-        <v>45624.67615214646</v>
+        <v>45647.03985265517</v>
       </c>
       <c r="F84" t="n">
         <v>240</v>
@@ -4392,7 +4392,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>45624.69049152695</v>
+        <v>45647.05419203566</v>
       </c>
     </row>
     <row r="85">
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="E85" s="2" t="n">
-        <v>45624.68104482323</v>
+        <v>45647.04474533194</v>
       </c>
       <c r="F85" t="n">
         <v>240</v>
@@ -4439,7 +4439,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>45624.69538420372</v>
+        <v>45647.05908471243</v>
       </c>
     </row>
     <row r="86">
@@ -4460,7 +4460,7 @@
         </is>
       </c>
       <c r="E86" s="2" t="n">
-        <v>45624.6859375</v>
+        <v>45647.04963800871</v>
       </c>
       <c r="F86" t="n">
         <v>240</v>
@@ -4486,7 +4486,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>45624.70027688049</v>
+        <v>45647.0639773892</v>
       </c>
     </row>
     <row r="87">
@@ -4507,7 +4507,7 @@
         </is>
       </c>
       <c r="E87" s="2" t="n">
-        <v>45624.69083017677</v>
+        <v>45647.05453068548</v>
       </c>
       <c r="F87" t="n">
         <v>105.3851638074757</v>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>45624.70516955726</v>
+        <v>45647.06887006597</v>
       </c>
     </row>
     <row r="88">
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="E88" s="2" t="n">
-        <v>45624.74716329964</v>
+        <v>45647.11086380835</v>
       </c>
       <c r="F88" t="n">
         <v>240</v>
@@ -4580,7 +4580,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>45624.76139066289</v>
+        <v>45647.12509117161</v>
       </c>
     </row>
     <row r="89">
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="E89" s="2" t="n">
-        <v>45624.75205597641</v>
+        <v>45647.11575648512</v>
       </c>
       <c r="F89" t="n">
         <v>240</v>
@@ -4627,7 +4627,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>45624.76628333966</v>
+        <v>45647.12998384838</v>
       </c>
     </row>
     <row r="90">
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="E90" s="2" t="n">
-        <v>45624.75694865318</v>
+        <v>45647.1206491619</v>
       </c>
       <c r="F90" t="n">
         <v>240</v>
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>45624.77117601644</v>
+        <v>45647.13487652515</v>
       </c>
     </row>
     <row r="91">
@@ -4695,7 +4695,7 @@
         </is>
       </c>
       <c r="E91" s="2" t="n">
-        <v>45624.76184132996</v>
+        <v>45647.12554183867</v>
       </c>
       <c r="F91" t="n">
         <v>240</v>
@@ -4721,7 +4721,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>45624.77606869321</v>
+        <v>45647.13976920192</v>
       </c>
     </row>
     <row r="92">
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="E92" s="2" t="n">
-        <v>45624.76673400673</v>
+        <v>45647.13043451544</v>
       </c>
       <c r="F92" t="n">
         <v>240</v>
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>45624.78096136998</v>
+        <v>45647.14466187869</v>
       </c>
     </row>
     <row r="93">
@@ -4789,7 +4789,7 @@
         </is>
       </c>
       <c r="E93" s="2" t="n">
-        <v>45624.7716266835</v>
+        <v>45647.13532719221</v>
       </c>
       <c r="F93" t="n">
         <v>240</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>45624.78585404675</v>
+        <v>45647.14955455546</v>
       </c>
     </row>
     <row r="94">
@@ -4836,7 +4836,7 @@
         </is>
       </c>
       <c r="E94" s="2" t="n">
-        <v>45624.77651936027</v>
+        <v>45647.14021986898</v>
       </c>
       <c r="F94" t="n">
         <v>240</v>
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>45624.79074672352</v>
+        <v>45647.15444723223</v>
       </c>
     </row>
     <row r="95">
@@ -4883,7 +4883,7 @@
         </is>
       </c>
       <c r="E95" s="2" t="n">
-        <v>45624.78141203704</v>
+        <v>45647.14511254575</v>
       </c>
       <c r="F95" t="n">
         <v>240</v>
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>45624.79563940029</v>
+        <v>45647.15933990901</v>
       </c>
     </row>
     <row r="96">
@@ -4930,7 +4930,7 @@
         </is>
       </c>
       <c r="E96" s="2" t="n">
-        <v>45624.78630471381</v>
+        <v>45647.15000522252</v>
       </c>
       <c r="F96" t="n">
         <v>240</v>
@@ -4956,7 +4956,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>45624.80053207706</v>
+        <v>45647.16423258578</v>
       </c>
     </row>
     <row r="97">
@@ -4977,7 +4977,7 @@
         </is>
       </c>
       <c r="E97" s="2" t="n">
-        <v>45624.79119739058</v>
+        <v>45647.15489789929</v>
       </c>
       <c r="F97" t="n">
         <v>240</v>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>45624.80542475383</v>
+        <v>45647.16912526255</v>
       </c>
     </row>
     <row r="98">
@@ -5024,7 +5024,7 @@
         </is>
       </c>
       <c r="E98" s="2" t="n">
-        <v>45624.79609006735</v>
+        <v>45647.15979057606</v>
       </c>
       <c r="F98" t="n">
         <v>240</v>
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>45624.8103174306</v>
+        <v>45647.17401793932</v>
       </c>
     </row>
     <row r="99">
@@ -5071,7 +5071,7 @@
         </is>
       </c>
       <c r="E99" s="2" t="n">
-        <v>45624.80098274412</v>
+        <v>45647.16468325283</v>
       </c>
       <c r="F99" t="n">
         <v>240</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>45624.81521010737</v>
+        <v>45647.17891061609</v>
       </c>
     </row>
     <row r="100">
@@ -5118,7 +5118,7 @@
         </is>
       </c>
       <c r="E100" s="2" t="n">
-        <v>45624.80587542089</v>
+        <v>45647.16957592961</v>
       </c>
       <c r="F100" t="n">
         <v>240</v>
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>45624.82010278414</v>
+        <v>45647.18380329286</v>
       </c>
     </row>
     <row r="101">
@@ -5165,7 +5165,7 @@
         </is>
       </c>
       <c r="E101" s="2" t="n">
-        <v>45624.81076809766</v>
+        <v>45647.17446860638</v>
       </c>
       <c r="F101" t="n">
         <v>240</v>
@@ -5191,7 +5191,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>45624.82499546091</v>
+        <v>45647.18869596963</v>
       </c>
     </row>
     <row r="102">
@@ -5212,7 +5212,7 @@
         </is>
       </c>
       <c r="E102" s="2" t="n">
-        <v>45624.81566077443</v>
+        <v>45647.17936128315</v>
       </c>
       <c r="F102" t="n">
         <v>240</v>
@@ -5238,7 +5238,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>45624.82988813768</v>
+        <v>45647.1935886464</v>
       </c>
     </row>
     <row r="103">
@@ -5259,7 +5259,7 @@
         </is>
       </c>
       <c r="E103" s="2" t="n">
-        <v>45624.8205534512</v>
+        <v>45647.18425395992</v>
       </c>
       <c r="F103" t="n">
         <v>240</v>
@@ -5285,7 +5285,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>45624.83478081445</v>
+        <v>45647.19848132317</v>
       </c>
     </row>
     <row r="104">
@@ -5306,7 +5306,7 @@
         </is>
       </c>
       <c r="E104" s="2" t="n">
-        <v>45624.82544612797</v>
+        <v>45647.18914663669</v>
       </c>
       <c r="F104" t="n">
         <v>240</v>
@@ -5332,7 +5332,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>45624.83967349122</v>
+        <v>45647.20337399994</v>
       </c>
     </row>
     <row r="105">
@@ -5353,7 +5353,7 @@
         </is>
       </c>
       <c r="E105" s="2" t="n">
-        <v>45624.83033880474</v>
+        <v>45647.19403931346</v>
       </c>
       <c r="F105" t="n">
         <v>240</v>
@@ -5379,7 +5379,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>45624.84456616799</v>
+        <v>45647.20826667672</v>
       </c>
     </row>
     <row r="106">
@@ -5400,7 +5400,7 @@
         </is>
       </c>
       <c r="E106" s="2" t="n">
-        <v>45624.83523148151</v>
+        <v>45647.19893199023</v>
       </c>
       <c r="F106" t="n">
         <v>154.6655064306469</v>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>45624.84945884477</v>
+        <v>45647.21315935349</v>
       </c>
     </row>
     <row r="107">
@@ -5447,7 +5447,7 @@
         </is>
       </c>
       <c r="E107" s="2" t="n">
-        <v>45625.1341887626</v>
+        <v>45647.49788927132</v>
       </c>
       <c r="F107" t="n">
         <v>240</v>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>45625.14980291689</v>
+        <v>45647.5135034256</v>
       </c>
     </row>
     <row r="108">
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="E108" s="2" t="n">
-        <v>45625.14040302976</v>
+        <v>45647.50410353847</v>
       </c>
       <c r="F108" t="n">
         <v>240</v>
@@ -5520,7 +5520,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>45625.15601718404</v>
+        <v>45647.51971769275</v>
       </c>
     </row>
     <row r="109">
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="E109" s="2" t="n">
-        <v>45625.14661729691</v>
+        <v>45647.51031780562</v>
       </c>
       <c r="F109" t="n">
         <v>240</v>
@@ -5567,7 +5567,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>45625.16223145119</v>
+        <v>45647.52593195991</v>
       </c>
     </row>
     <row r="110">
@@ -5588,7 +5588,7 @@
         </is>
       </c>
       <c r="E110" s="2" t="n">
-        <v>45625.15283156406</v>
+        <v>45647.51653207278</v>
       </c>
       <c r="F110" t="n">
         <v>240</v>
@@ -5614,7 +5614,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>45625.16844571834</v>
+        <v>45647.53214622706</v>
       </c>
     </row>
     <row r="111">
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="E111" s="2" t="n">
-        <v>45625.15904583121</v>
+        <v>45647.52274633993</v>
       </c>
       <c r="F111" t="n">
         <v>240</v>
@@ -5661,7 +5661,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>45625.1746599855</v>
+        <v>45647.53836049421</v>
       </c>
     </row>
     <row r="112">
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="E112" s="2" t="n">
-        <v>45625.16526009837</v>
+        <v>45647.52896060708</v>
       </c>
       <c r="F112" t="n">
         <v>240</v>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>45625.18087425265</v>
+        <v>45647.54457476136</v>
       </c>
     </row>
     <row r="113">
@@ -5729,7 +5729,7 @@
         </is>
       </c>
       <c r="E113" s="2" t="n">
-        <v>45625.17147436552</v>
+        <v>45647.53517487424</v>
       </c>
       <c r="F113" t="n">
         <v>240</v>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>45625.1870885198</v>
+        <v>45647.55078902852</v>
       </c>
     </row>
     <row r="114">
@@ -5776,7 +5776,7 @@
         </is>
       </c>
       <c r="E114" s="2" t="n">
-        <v>45625.17768863268</v>
+        <v>45647.54138914139</v>
       </c>
       <c r="F114" t="n">
         <v>240</v>
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>45625.19330278695</v>
+        <v>45647.55700329567</v>
       </c>
     </row>
     <row r="115">
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="E115" s="2" t="n">
-        <v>45625.18390289983</v>
+        <v>45647.54760340854</v>
       </c>
       <c r="F115" t="n">
         <v>187.288847561394</v>
@@ -5849,7 +5849,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>45625.19951705411</v>
+        <v>45647.56321756283</v>
       </c>
     </row>
     <row r="116">
@@ -5870,7 +5870,7 @@
         </is>
       </c>
       <c r="E116" s="2" t="n">
-        <v>45625.60811237372</v>
+        <v>45647.97181288243</v>
       </c>
       <c r="F116" t="n">
         <v>240</v>
@@ -5896,7 +5896,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>45625.6223332704</v>
+        <v>45647.98603377912</v>
       </c>
     </row>
     <row r="117">
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="E117" s="2" t="n">
-        <v>45625.61300505049</v>
+        <v>45647.9767055592</v>
       </c>
       <c r="F117" t="n">
         <v>240</v>
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>45625.62722594717</v>
+        <v>45647.99092645589</v>
       </c>
     </row>
     <row r="118">
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="E118" s="2" t="n">
-        <v>45625.61789772726</v>
+        <v>45647.98159823597</v>
       </c>
       <c r="F118" t="n">
         <v>240</v>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>45625.63211862394</v>
+        <v>45647.99581913266</v>
       </c>
     </row>
     <row r="119">
@@ -6011,7 +6011,7 @@
         </is>
       </c>
       <c r="E119" s="2" t="n">
-        <v>45625.62279040403</v>
+        <v>45647.98649091274</v>
       </c>
       <c r="F119" t="n">
         <v>240</v>
@@ -6037,7 +6037,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>45625.63701130071</v>
+        <v>45648.00071180944</v>
       </c>
     </row>
     <row r="120">
@@ -6058,7 +6058,7 @@
         </is>
       </c>
       <c r="E120" s="2" t="n">
-        <v>45625.6276830808</v>
+        <v>45647.99138358951</v>
       </c>
       <c r="F120" t="n">
         <v>240</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>45625.64190397749</v>
+        <v>45648.00560448621</v>
       </c>
     </row>
     <row r="121">
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="E121" s="2" t="n">
-        <v>45625.63257575757</v>
+        <v>45647.99627626628</v>
       </c>
       <c r="F121" t="n">
         <v>240</v>
@@ -6131,7 +6131,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>45625.64679665426</v>
+        <v>45648.01049716298</v>
       </c>
     </row>
     <row r="122">
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="E122" s="2" t="n">
-        <v>45625.63746843434</v>
+        <v>45648.00116894305</v>
       </c>
       <c r="F122" t="n">
         <v>240</v>
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>45625.65168933103</v>
+        <v>45648.01538983975</v>
       </c>
     </row>
     <row r="123">
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="E123" s="2" t="n">
-        <v>45625.64236111111</v>
+        <v>45648.00606161982</v>
       </c>
       <c r="F123" t="n">
         <v>240</v>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>45625.6565820078</v>
+        <v>45648.02028251652</v>
       </c>
     </row>
     <row r="124">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="E124" s="2" t="n">
-        <v>45625.64725378788</v>
+        <v>45648.01095429659</v>
       </c>
       <c r="F124" t="n">
         <v>240</v>
@@ -6272,7 +6272,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>45625.66147468457</v>
+        <v>45648.02517519329</v>
       </c>
     </row>
     <row r="125">
@@ -6293,7 +6293,7 @@
         </is>
       </c>
       <c r="E125" s="2" t="n">
-        <v>45625.65214646465</v>
+        <v>45648.01584697337</v>
       </c>
       <c r="F125" t="n">
         <v>240</v>
@@ -6319,7 +6319,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>45625.66636736134</v>
+        <v>45648.03006787006</v>
       </c>
     </row>
     <row r="126">
@@ -6340,7 +6340,7 @@
         </is>
       </c>
       <c r="E126" s="2" t="n">
-        <v>45625.65703914142</v>
+        <v>45648.02073965014</v>
       </c>
       <c r="F126" t="n">
         <v>240</v>
@@ -6366,7 +6366,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>45625.67126003811</v>
+        <v>45648.03496054683</v>
       </c>
     </row>
     <row r="127">
@@ -6387,7 +6387,7 @@
         </is>
       </c>
       <c r="E127" s="2" t="n">
-        <v>45625.66193181819</v>
+        <v>45648.02563232691</v>
       </c>
       <c r="F127" t="n">
         <v>240</v>
@@ -6413,7 +6413,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>45625.67615271488</v>
+        <v>45648.0398532236</v>
       </c>
     </row>
     <row r="128">
@@ -6434,7 +6434,7 @@
         </is>
       </c>
       <c r="E128" s="2" t="n">
-        <v>45625.66682449497</v>
+        <v>45648.03052500368</v>
       </c>
       <c r="F128" t="n">
         <v>240</v>
@@ -6460,7 +6460,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>45625.68104539166</v>
+        <v>45648.04474590037</v>
       </c>
     </row>
     <row r="129">
@@ -6481,7 +6481,7 @@
         </is>
       </c>
       <c r="E129" s="2" t="n">
-        <v>45625.67001052186</v>
+        <v>45648.03371103058</v>
       </c>
       <c r="F129" t="n">
         <v>240</v>
@@ -6507,7 +6507,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>45625.68427445512</v>
+        <v>45648.04797496384</v>
       </c>
     </row>
     <row r="130">
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="E130" s="2" t="n">
-        <v>45625.67171717174</v>
+        <v>45648.03541768045</v>
       </c>
       <c r="F130" t="n">
         <v>240</v>
@@ -6554,7 +6554,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>45625.68593806843</v>
+        <v>45648.04963857714</v>
       </c>
     </row>
     <row r="131">
@@ -6575,7 +6575,7 @@
         </is>
       </c>
       <c r="E131" s="2" t="n">
-        <v>45625.67490319863</v>
+        <v>45648.03860370735</v>
       </c>
       <c r="F131" t="n">
         <v>240</v>
@@ -6601,7 +6601,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>45625.6891671319</v>
+        <v>45648.05286764061</v>
       </c>
     </row>
     <row r="132">
@@ -6622,7 +6622,7 @@
         </is>
       </c>
       <c r="E132" s="2" t="n">
-        <v>45625.6797958754</v>
+        <v>45648.04349638412</v>
       </c>
       <c r="F132" t="n">
         <v>240</v>
@@ -6648,7 +6648,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>45625.69405980867</v>
+        <v>45648.05776031739</v>
       </c>
     </row>
     <row r="133">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="E133" s="2" t="n">
-        <v>45625.68468855217</v>
+        <v>45648.04838906089</v>
       </c>
       <c r="F133" t="n">
         <v>240</v>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>45625.69895248544</v>
+        <v>45648.06265299416</v>
       </c>
     </row>
     <row r="134">
@@ -6716,7 +6716,7 @@
         </is>
       </c>
       <c r="E134" s="2" t="n">
-        <v>45625.68958122894</v>
+        <v>45648.05328173766</v>
       </c>
       <c r="F134" t="n">
         <v>240</v>
@@ -6742,7 +6742,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>45625.70384516221</v>
+        <v>45648.06754567093</v>
       </c>
     </row>
     <row r="135">
@@ -6763,7 +6763,7 @@
         </is>
       </c>
       <c r="E135" s="2" t="n">
-        <v>45625.69447390571</v>
+        <v>45648.05817441444</v>
       </c>
       <c r="F135" t="n">
         <v>240</v>
@@ -6789,7 +6789,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>45625.70873783898</v>
+        <v>45648.0724383477</v>
       </c>
     </row>
     <row r="136">
@@ -6810,7 +6810,7 @@
         </is>
       </c>
       <c r="E136" s="2" t="n">
-        <v>45625.69936658248</v>
+        <v>45648.06306709121</v>
       </c>
       <c r="F136" t="n">
         <v>240</v>
@@ -6836,7 +6836,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>45625.71363051575</v>
+        <v>45648.07733102447</v>
       </c>
     </row>
     <row r="137">
@@ -6857,7 +6857,7 @@
         </is>
       </c>
       <c r="E137" s="2" t="n">
-        <v>45625.70425925926</v>
+        <v>45648.06795976798</v>
       </c>
       <c r="F137" t="n">
         <v>240</v>
@@ -6883,7 +6883,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>45625.71852319253</v>
+        <v>45648.08222370124</v>
       </c>
     </row>
     <row r="138">
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="E138" s="2" t="n">
-        <v>45625.70915193603</v>
+        <v>45648.07285244475</v>
       </c>
       <c r="F138" t="n">
         <v>240</v>
@@ -6930,7 +6930,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>45625.7234158693</v>
+        <v>45648.08711637801</v>
       </c>
     </row>
     <row r="139">
@@ -6951,7 +6951,7 @@
         </is>
       </c>
       <c r="E139" s="2" t="n">
-        <v>45625.7140446128</v>
+        <v>45648.07774512152</v>
       </c>
       <c r="F139" t="n">
         <v>240</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>45625.72830854607</v>
+        <v>45648.09200905478</v>
       </c>
     </row>
     <row r="140">
@@ -6998,7 +6998,7 @@
         </is>
       </c>
       <c r="E140" s="2" t="n">
-        <v>45625.71893728957</v>
+        <v>45648.08263779829</v>
       </c>
       <c r="F140" t="n">
         <v>240</v>
@@ -7024,7 +7024,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>45625.73320122284</v>
+        <v>45648.09690173155</v>
       </c>
     </row>
     <row r="141">
@@ -7045,7 +7045,7 @@
         </is>
       </c>
       <c r="E141" s="2" t="n">
-        <v>45625.72382996634</v>
+        <v>45648.08753047506</v>
       </c>
       <c r="F141" t="n">
         <v>240</v>
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>45625.73809389961</v>
+        <v>45648.10179440832</v>
       </c>
     </row>
     <row r="142">
@@ -7092,7 +7092,7 @@
         </is>
       </c>
       <c r="E142" s="2" t="n">
-        <v>45625.72872264311</v>
+        <v>45648.09242315183</v>
       </c>
       <c r="F142" t="n">
         <v>240</v>
@@ -7118,7 +7118,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>45625.74298657638</v>
+        <v>45648.10668708509</v>
       </c>
     </row>
     <row r="143">
@@ -7139,7 +7139,7 @@
         </is>
       </c>
       <c r="E143" s="2" t="n">
-        <v>45625.73361531988</v>
+        <v>45648.0973158286</v>
       </c>
       <c r="F143" t="n">
         <v>240</v>
@@ -7165,7 +7165,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>45625.74787925315</v>
+        <v>45648.11157976186</v>
       </c>
     </row>
     <row r="144">
@@ -7186,7 +7186,7 @@
         </is>
       </c>
       <c r="E144" s="2" t="n">
-        <v>45625.73850799666</v>
+        <v>45648.10220850537</v>
       </c>
       <c r="F144" t="n">
         <v>240</v>
@@ -7212,7 +7212,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>45625.75277192992</v>
+        <v>45648.11647243863</v>
       </c>
     </row>
     <row r="145">
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="E145" s="2" t="n">
-        <v>45625.74340067343</v>
+        <v>45648.10710118214</v>
       </c>
       <c r="F145" t="n">
         <v>240</v>
@@ -7259,7 +7259,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>45625.75766460669</v>
+        <v>45648.1213651154</v>
       </c>
     </row>
     <row r="146">
@@ -7280,7 +7280,7 @@
         </is>
       </c>
       <c r="E146" s="2" t="n">
-        <v>45625.7482933502</v>
+        <v>45648.11199385891</v>
       </c>
       <c r="F146" t="n">
         <v>240</v>
@@ -7306,7 +7306,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>45625.76255728346</v>
+        <v>45648.12625779217</v>
       </c>
     </row>
     <row r="147">
@@ -7327,7 +7327,7 @@
         </is>
       </c>
       <c r="E147" s="2" t="n">
-        <v>45625.75318602697</v>
+        <v>45648.11688653568</v>
       </c>
       <c r="F147" t="n">
         <v>240</v>
@@ -7353,7 +7353,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>45625.76744996023</v>
+        <v>45648.13115046894</v>
       </c>
     </row>
     <row r="148">
@@ -7374,7 +7374,7 @@
         </is>
       </c>
       <c r="E148" s="2" t="n">
-        <v>45625.75807870374</v>
+        <v>45648.12177921245</v>
       </c>
       <c r="F148" t="n">
         <v>240</v>
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>45625.772342637</v>
+        <v>45648.13604314571</v>
       </c>
     </row>
     <row r="149">
@@ -7421,7 +7421,7 @@
         </is>
       </c>
       <c r="E149" s="2" t="n">
-        <v>45625.76297138051</v>
+        <v>45648.12667188922</v>
       </c>
       <c r="F149" t="n">
         <v>240</v>
@@ -7447,7 +7447,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>45625.77723531377</v>
+        <v>45648.14093582249</v>
       </c>
     </row>
     <row r="150">
@@ -7468,7 +7468,7 @@
         </is>
       </c>
       <c r="E150" s="2" t="n">
-        <v>45625.76786405728</v>
+        <v>45648.13156456599</v>
       </c>
       <c r="F150" t="n">
         <v>240</v>
@@ -7494,7 +7494,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>45625.78212799055</v>
+        <v>45648.14582849926</v>
       </c>
     </row>
     <row r="151">
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="E151" s="2" t="n">
-        <v>45625.77275673405</v>
+        <v>45648.13645724276</v>
       </c>
       <c r="F151" t="n">
         <v>240</v>
@@ -7541,7 +7541,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>45625.78702066732</v>
+        <v>45648.15072117603</v>
       </c>
     </row>
     <row r="152">
@@ -7562,7 +7562,7 @@
         </is>
       </c>
       <c r="E152" s="2" t="n">
-        <v>45625.77764941082</v>
+        <v>45648.14134991954</v>
       </c>
       <c r="F152" t="n">
         <v>240</v>
@@ -7588,7 +7588,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>45625.79191334409</v>
+        <v>45648.1556138528</v>
       </c>
     </row>
     <row r="153">
@@ -7609,7 +7609,7 @@
         </is>
       </c>
       <c r="E153" s="2" t="n">
-        <v>45625.7825420876</v>
+        <v>45648.14624259631</v>
       </c>
       <c r="F153" t="n">
         <v>240</v>
@@ -7635,7 +7635,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>45625.79680602086</v>
+        <v>45648.16050652957</v>
       </c>
     </row>
     <row r="154">
@@ -7656,7 +7656,7 @@
         </is>
       </c>
       <c r="E154" s="2" t="n">
-        <v>45625.78743476437</v>
+        <v>45648.15113527308</v>
       </c>
       <c r="F154" t="n">
         <v>240</v>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>45625.80169869763</v>
+        <v>45648.16539920634</v>
       </c>
     </row>
     <row r="155">
@@ -7703,7 +7703,7 @@
         </is>
       </c>
       <c r="E155" s="2" t="n">
-        <v>45625.79232744114</v>
+        <v>45648.15602794985</v>
       </c>
       <c r="F155" t="n">
         <v>240</v>
@@ -7729,7 +7729,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>45625.8065913744</v>
+        <v>45648.17029188311</v>
       </c>
     </row>
     <row r="156">
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="E156" s="2" t="n">
-        <v>45625.79722011791</v>
+        <v>45648.16092062662</v>
       </c>
       <c r="F156" t="n">
         <v>240</v>
@@ -7776,7 +7776,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>45625.81148405117</v>
+        <v>45648.17518455988</v>
       </c>
     </row>
     <row r="157">
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="E157" s="2" t="n">
-        <v>45625.80211279468</v>
+        <v>45648.16581330339</v>
       </c>
       <c r="F157" t="n">
         <v>240</v>
@@ -7823,7 +7823,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>45625.81637672794</v>
+        <v>45648.18007723666</v>
       </c>
     </row>
     <row r="158">
@@ -7844,7 +7844,7 @@
         </is>
       </c>
       <c r="E158" s="2" t="n">
-        <v>45625.80700547145</v>
+        <v>45648.17070598016</v>
       </c>
       <c r="F158" t="n">
         <v>240</v>
@@ -7870,7 +7870,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>45625.82126940471</v>
+        <v>45648.18496991343</v>
       </c>
     </row>
     <row r="159">
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="E159" s="2" t="n">
-        <v>45625.81189814822</v>
+        <v>45648.17559865693</v>
       </c>
       <c r="F159" t="n">
         <v>240</v>
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>45625.82616208148</v>
+        <v>45648.1898625902</v>
       </c>
     </row>
     <row r="160">
@@ -7938,7 +7938,7 @@
         </is>
       </c>
       <c r="E160" s="2" t="n">
-        <v>45625.81679082499</v>
+        <v>45648.1804913337</v>
       </c>
       <c r="F160" t="n">
         <v>240</v>
@@ -7964,7 +7964,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>45625.83105475825</v>
+        <v>45648.19475526697</v>
       </c>
     </row>
     <row r="161">
@@ -7985,7 +7985,7 @@
         </is>
       </c>
       <c r="E161" s="2" t="n">
-        <v>45625.82168350176</v>
+        <v>45648.18538401047</v>
       </c>
       <c r="F161" t="n">
         <v>240</v>
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>45625.83594743502</v>
+        <v>45648.19964794374</v>
       </c>
     </row>
     <row r="162">
@@ -8032,7 +8032,7 @@
         </is>
       </c>
       <c r="E162" s="2" t="n">
-        <v>45625.82657617853</v>
+        <v>45648.19027668724</v>
       </c>
       <c r="F162" t="n">
         <v>240</v>
@@ -8058,7 +8058,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>45625.84084011179</v>
+        <v>45648.20454062051</v>
       </c>
     </row>
     <row r="163">
@@ -8079,7 +8079,7 @@
         </is>
       </c>
       <c r="E163" s="2" t="n">
-        <v>45625.8314688553</v>
+        <v>45648.19516936401</v>
       </c>
       <c r="F163" t="n">
         <v>240</v>
@@ -8105,7 +8105,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>45625.84573278856</v>
+        <v>45648.20943329728</v>
       </c>
     </row>
     <row r="164">
@@ -8126,7 +8126,7 @@
         </is>
       </c>
       <c r="E164" s="2" t="n">
-        <v>45625.83636153207</v>
+        <v>45648.20006204079</v>
       </c>
       <c r="F164" t="n">
         <v>240</v>
@@ -8152,7 +8152,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>45625.85062546533</v>
+        <v>45648.21432597405</v>
       </c>
     </row>
     <row r="165">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="E165" s="2" t="n">
-        <v>45625.84125420884</v>
+        <v>45648.20495471756</v>
       </c>
       <c r="F165" t="n">
         <v>106.1065032196875</v>
@@ -8199,7 +8199,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>45625.8555181421</v>
+        <v>45648.21921865082</v>
       </c>
     </row>
     <row r="166">
@@ -8220,7 +8220,7 @@
         </is>
       </c>
       <c r="E166" s="2" t="n">
-        <v>45626.12751052187</v>
+        <v>45648.49121103058</v>
       </c>
       <c r="F166" t="n">
         <v>240</v>
@@ -8246,7 +8246,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>45626.14164094478</v>
+        <v>45648.50534145349</v>
       </c>
     </row>
     <row r="167">
@@ -8267,7 +8267,7 @@
         </is>
       </c>
       <c r="E167" s="2" t="n">
-        <v>45626.13240319864</v>
+        <v>45648.49610370735</v>
       </c>
       <c r="F167" t="n">
         <v>240</v>
@@ -8293,7 +8293,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>45626.14653362155</v>
+        <v>45648.51023413026</v>
       </c>
     </row>
     <row r="168">
@@ -8314,7 +8314,7 @@
         </is>
       </c>
       <c r="E168" s="2" t="n">
-        <v>45626.13729587541</v>
+        <v>45648.50099638412</v>
       </c>
       <c r="F168" t="n">
         <v>240</v>
@@ -8340,7 +8340,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>45626.15142629832</v>
+        <v>45648.51512680704</v>
       </c>
     </row>
     <row r="169">
@@ -8361,7 +8361,7 @@
         </is>
       </c>
       <c r="E169" s="2" t="n">
-        <v>45626.14218855218</v>
+        <v>45648.50588906089</v>
       </c>
       <c r="F169" t="n">
         <v>240</v>
@@ -8387,7 +8387,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>45626.1563189751</v>
+        <v>45648.52001948381</v>
       </c>
     </row>
     <row r="170">
@@ -8408,7 +8408,7 @@
         </is>
       </c>
       <c r="E170" s="2" t="n">
-        <v>45626.14708122895</v>
+        <v>45648.51078173766</v>
       </c>
       <c r="F170" t="n">
         <v>240</v>
@@ -8434,7 +8434,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>45626.16121165187</v>
+        <v>45648.52491216058</v>
       </c>
     </row>
     <row r="171">
@@ -8455,7 +8455,7 @@
         </is>
       </c>
       <c r="E171" s="2" t="n">
-        <v>45626.15197390572</v>
+        <v>45648.51567441443</v>
       </c>
       <c r="F171" t="n">
         <v>240</v>
@@ -8481,7 +8481,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>45626.16610432864</v>
+        <v>45648.52980483735</v>
       </c>
     </row>
     <row r="172">
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="E172" s="2" t="n">
-        <v>45626.15686658249</v>
+        <v>45648.5205670912</v>
       </c>
       <c r="F172" t="n">
         <v>240</v>
@@ -8528,7 +8528,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>45626.17099700541</v>
+        <v>45648.53469751412</v>
       </c>
     </row>
     <row r="173">
@@ -8549,7 +8549,7 @@
         </is>
       </c>
       <c r="E173" s="2" t="n">
-        <v>45626.16175925926</v>
+        <v>45648.52545976797</v>
       </c>
       <c r="F173" t="n">
         <v>240</v>
@@ -8575,7 +8575,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>45626.17588968218</v>
+        <v>45648.53959019089</v>
       </c>
     </row>
     <row r="174">
@@ -8596,7 +8596,7 @@
         </is>
       </c>
       <c r="E174" s="2" t="n">
-        <v>45626.16665193603</v>
+        <v>45648.53035244474</v>
       </c>
       <c r="F174" t="n">
         <v>240</v>
@@ -8622,7 +8622,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>45626.18078235895</v>
+        <v>45648.54448286766</v>
       </c>
     </row>
     <row r="175">
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="E175" s="2" t="n">
-        <v>45626.1715446128</v>
+        <v>45648.53524512151</v>
       </c>
       <c r="F175" t="n">
         <v>240</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>45626.18567503572</v>
+        <v>45648.54937554443</v>
       </c>
     </row>
     <row r="176">
@@ -8690,7 +8690,7 @@
         </is>
       </c>
       <c r="E176" s="2" t="n">
-        <v>45626.17643728957</v>
+        <v>45648.54013779829</v>
       </c>
       <c r="F176" t="n">
         <v>240</v>
@@ -8716,7 +8716,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>45626.19056771249</v>
+        <v>45648.5542682212</v>
       </c>
     </row>
     <row r="177">
@@ -8737,7 +8737,7 @@
         </is>
       </c>
       <c r="E177" s="2" t="n">
-        <v>45626.18132996634</v>
+        <v>45648.54503047506</v>
       </c>
       <c r="F177" t="n">
         <v>240</v>
@@ -8763,7 +8763,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>45626.19546038926</v>
+        <v>45648.55916089797</v>
       </c>
     </row>
     <row r="178">
@@ -8784,7 +8784,7 @@
         </is>
       </c>
       <c r="E178" s="2" t="n">
-        <v>45626.18622264311</v>
+        <v>45648.54992315183</v>
       </c>
       <c r="F178" t="n">
         <v>240</v>
@@ -8810,7 +8810,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>45626.20035306603</v>
+        <v>45648.56405357474</v>
       </c>
     </row>
     <row r="179">
@@ -8831,7 +8831,7 @@
         </is>
       </c>
       <c r="E179" s="2" t="n">
-        <v>45626.19111531988</v>
+        <v>45648.5548158286</v>
       </c>
       <c r="F179" t="n">
         <v>240</v>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>45626.2052457428</v>
+        <v>45648.56894625151</v>
       </c>
     </row>
     <row r="180">
@@ -8878,7 +8878,7 @@
         </is>
       </c>
       <c r="E180" s="2" t="n">
-        <v>45626.19600799665</v>
+        <v>45648.55970850537</v>
       </c>
       <c r="F180" t="n">
         <v>240</v>
@@ -8904,7 +8904,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>45626.21013841957</v>
+        <v>45648.57383892829</v>
       </c>
     </row>
     <row r="181">
@@ -8925,7 +8925,7 @@
         </is>
       </c>
       <c r="E181" s="2" t="n">
-        <v>45626.20090067342</v>
+        <v>45648.56460118214</v>
       </c>
       <c r="F181" t="n">
         <v>240</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>45626.21503109634</v>
+        <v>45648.57873160506</v>
       </c>
     </row>
     <row r="182">
@@ -8972,7 +8972,7 @@
         </is>
       </c>
       <c r="E182" s="2" t="n">
-        <v>45626.2057933502</v>
+        <v>45648.56949385891</v>
       </c>
       <c r="F182" t="n">
         <v>240</v>
@@ -8998,7 +8998,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>45626.21992377311</v>
+        <v>45648.58362428183</v>
       </c>
     </row>
     <row r="183">
@@ -9019,7 +9019,7 @@
         </is>
       </c>
       <c r="E183" s="2" t="n">
-        <v>45626.21068602697</v>
+        <v>45648.57438653569</v>
       </c>
       <c r="F183" t="n">
         <v>240</v>
@@ -9045,7 +9045,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>45626.22481644988</v>
+        <v>45648.5885169586</v>
       </c>
     </row>
     <row r="184">
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="E184" s="2" t="n">
-        <v>45626.21068602697</v>
+        <v>45648.57438653569</v>
       </c>
       <c r="F184" t="n">
         <v>184.5631398016703</v>
@@ -9092,7 +9092,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>45626.22481644988</v>
+        <v>45648.5885169586</v>
       </c>
     </row>
     <row r="185">
